--- a/dim/dim_calendario_eventos.xlsx
+++ b/dim/dim_calendario_eventos.xlsx
@@ -5,24 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\SP46128684\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\SP44812227\Documents\01_ProyecVenta\dim\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10512"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10510"/>
   </bookViews>
   <sheets>
     <sheet name="eventos" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">eventos!$A$1:$C$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">eventos!$A$1:$F$115</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="25">
   <si>
     <t>fecha</t>
   </si>
@@ -89,6 +90,15 @@
   <si>
     <t>año_nuevo_eve</t>
   </si>
+  <si>
+    <t>mes</t>
+  </si>
+  <si>
+    <t>año</t>
+  </si>
+  <si>
+    <t>periodo</t>
+  </si>
 </sst>
 </file>
 
@@ -123,9 +133,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,1284 +439,2761 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F115"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="17" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45292</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2">
+        <f>+MONTH(A2)</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="2">
+        <f>YEAR(A2)</f>
+        <v>2024</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>TEXT(A2,"YYYYMM")</f>
+        <v>202401</v>
+      </c>
+      <c r="E2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45306</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
+        <f t="shared" ref="B3:B66" si="0">+MONTH(A3)</f>
+        <v>1</v>
+      </c>
+      <c r="C3" s="2">
+        <f t="shared" ref="C3:C66" si="1">YEAR(A3)</f>
+        <v>2024</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f t="shared" ref="D3:D66" si="2">TEXT(A3,"YYYYMM")</f>
+        <v>202401</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45322</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202401</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45336</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202402</v>
+      </c>
+      <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45337</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202402</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45351</v>
       </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202402</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45366</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202403</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45375</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202403</v>
+      </c>
+      <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45379</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202403</v>
+      </c>
+      <c r="E10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>45380</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202403</v>
+      </c>
+      <c r="E11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>45382</v>
       </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202403</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>45397</v>
       </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202404</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>45412</v>
       </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202404</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>45424</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202405</v>
+      </c>
+      <c r="E15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>45427</v>
       </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202405</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>45443</v>
       </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202405</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>45458</v>
       </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C18" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202406</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>45459</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C19" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202406</v>
+      </c>
+      <c r="E19" t="s">
         <v>15</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>45473</v>
       </c>
-      <c r="B20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C20" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202406</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>45488</v>
       </c>
-      <c r="B21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C21" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202407</v>
+      </c>
+      <c r="E21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>45501</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C22" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202407</v>
+      </c>
+      <c r="E22" t="s">
         <v>16</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>45502</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C23" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202407</v>
+      </c>
+      <c r="E23" t="s">
         <v>16</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>45504</v>
       </c>
-      <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202407</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>45519</v>
       </c>
-      <c r="B25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202408</v>
+      </c>
+      <c r="E25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>45535</v>
       </c>
-      <c r="B26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C26" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202408</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>45550</v>
       </c>
-      <c r="B27" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202409</v>
+      </c>
+      <c r="E27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>45550</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C28" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202409</v>
+      </c>
+      <c r="E28" t="s">
         <v>17</v>
       </c>
-      <c r="C28" t="s">
+      <c r="F28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>45565</v>
       </c>
-      <c r="B29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C29" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202409</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>45580</v>
       </c>
-      <c r="B30" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C30" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202410</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>45596</v>
       </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C31" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202410</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>45596</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C32" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202410</v>
+      </c>
+      <c r="E32" t="s">
         <v>18</v>
       </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>45611</v>
       </c>
-      <c r="B33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B33" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C33" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202411</v>
+      </c>
+      <c r="E33" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>45625</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C34" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202411</v>
+      </c>
+      <c r="E34" t="s">
         <v>19</v>
       </c>
-      <c r="C34" t="s">
+      <c r="F34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>45626</v>
       </c>
-      <c r="B35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C35" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202411</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>45641</v>
       </c>
-      <c r="B36" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B36" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C36" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D36" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202412</v>
+      </c>
+      <c r="E36" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>45651</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C37" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202412</v>
+      </c>
+      <c r="E37" t="s">
         <v>20</v>
       </c>
-      <c r="C37" t="s">
+      <c r="F37" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>45657</v>
       </c>
-      <c r="B38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C38" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202412</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>45657</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C39" s="2">
+        <f t="shared" si="1"/>
+        <v>2024</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202412</v>
+      </c>
+      <c r="E39" t="s">
         <v>21</v>
       </c>
-      <c r="C39" t="s">
+      <c r="F39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>45658</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C40" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202501</v>
+      </c>
+      <c r="E40" t="s">
         <v>3</v>
       </c>
-      <c r="C40" t="s">
+      <c r="F40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>45672</v>
       </c>
-      <c r="B41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B41" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C41" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202501</v>
+      </c>
+      <c r="E41" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>45688</v>
       </c>
-      <c r="B42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C42" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202501</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>45702</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C43" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202502</v>
+      </c>
+      <c r="E43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="F43" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>45703</v>
       </c>
-      <c r="B44" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B44" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C44" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202502</v>
+      </c>
+      <c r="E44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>45716</v>
       </c>
-      <c r="B45" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B45" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C45" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202502</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45731</v>
       </c>
-      <c r="B46" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B46" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C46" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202503</v>
+      </c>
+      <c r="E46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>45747</v>
       </c>
-      <c r="B47" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B47" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C47" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202503</v>
+      </c>
+      <c r="E47" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>45760</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C48" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202504</v>
+      </c>
+      <c r="E48" t="s">
         <v>10</v>
       </c>
-      <c r="C48" t="s">
+      <c r="F48" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>45762</v>
       </c>
-      <c r="B49" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C49" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202504</v>
+      </c>
+      <c r="E49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>45764</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C50" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D50" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202504</v>
+      </c>
+      <c r="E50" t="s">
         <v>12</v>
       </c>
-      <c r="C50" t="s">
+      <c r="F50" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>45765</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C51" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D51" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202504</v>
+      </c>
+      <c r="E51" t="s">
         <v>13</v>
       </c>
-      <c r="C51" t="s">
+      <c r="F51" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>45777</v>
       </c>
-      <c r="B52" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B52" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C52" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D52" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202504</v>
+      </c>
+      <c r="E52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>45788</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C53" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D53" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202505</v>
+      </c>
+      <c r="E53" t="s">
         <v>14</v>
       </c>
-      <c r="C53" t="s">
+      <c r="F53" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>45792</v>
       </c>
-      <c r="B54" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B54" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C54" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D54" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202505</v>
+      </c>
+      <c r="E54" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>45808</v>
       </c>
-      <c r="B55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B55" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C55" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D55" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202505</v>
+      </c>
+      <c r="E55" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>45823</v>
       </c>
-      <c r="B56" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B56" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C56" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202506</v>
+      </c>
+      <c r="E56" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>45823</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C57" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202506</v>
+      </c>
+      <c r="E57" t="s">
         <v>15</v>
       </c>
-      <c r="C57" t="s">
+      <c r="F57" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>45838</v>
       </c>
-      <c r="B58" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B58" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C58" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D58" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202506</v>
+      </c>
+      <c r="E58" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>45853</v>
       </c>
-      <c r="B59" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B59" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C59" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D59" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202507</v>
+      </c>
+      <c r="E59" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>45866</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C60" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D60" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202507</v>
+      </c>
+      <c r="E60" t="s">
         <v>16</v>
       </c>
-      <c r="C60" t="s">
+      <c r="F60" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>45867</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C61" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D61" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202507</v>
+      </c>
+      <c r="E61" t="s">
         <v>16</v>
       </c>
-      <c r="C61" t="s">
+      <c r="F61" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>45869</v>
       </c>
-      <c r="B62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B62" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C62" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D62" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202507</v>
+      </c>
+      <c r="E62" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>45884</v>
       </c>
-      <c r="B63" t="s">
-        <v>5</v>
-      </c>
-      <c r="C63" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B63" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C63" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D63" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202508</v>
+      </c>
+      <c r="E63" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>45900</v>
       </c>
-      <c r="B64" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B64" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C64" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D64" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202508</v>
+      </c>
+      <c r="E64" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>45915</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C65" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D65" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202509</v>
+      </c>
+      <c r="E65" t="s">
         <v>17</v>
       </c>
-      <c r="C65" t="s">
+      <c r="F65" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>45915</v>
       </c>
-      <c r="B66" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B66" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C66" s="2">
+        <f t="shared" si="1"/>
+        <v>2025</v>
+      </c>
+      <c r="D66" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>202509</v>
+      </c>
+      <c r="E66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>45930</v>
       </c>
-      <c r="B67" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B67" s="2">
+        <f t="shared" ref="B67:B115" si="3">+MONTH(A67)</f>
+        <v>9</v>
+      </c>
+      <c r="C67" s="2">
+        <f t="shared" ref="C67:C115" si="4">YEAR(A67)</f>
+        <v>2025</v>
+      </c>
+      <c r="D67" s="2" t="str">
+        <f t="shared" ref="D67:D115" si="5">TEXT(A67,"YYYYMM")</f>
+        <v>202509</v>
+      </c>
+      <c r="E67" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>45945</v>
       </c>
-      <c r="B68" t="s">
-        <v>5</v>
-      </c>
-      <c r="C68" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B68" s="2">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="C68" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D68" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202510</v>
+      </c>
+      <c r="E68" t="s">
+        <v>5</v>
+      </c>
+      <c r="F68" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>45961</v>
       </c>
-      <c r="B69" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B69" s="2">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="C69" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D69" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202510</v>
+      </c>
+      <c r="E69" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>45961</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="2">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="C70" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D70" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202510</v>
+      </c>
+      <c r="E70" t="s">
         <v>18</v>
       </c>
-      <c r="C70" t="s">
+      <c r="F70" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>45976</v>
       </c>
-      <c r="B71" t="s">
-        <v>5</v>
-      </c>
-      <c r="C71" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B71" s="2">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="C71" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D71" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202511</v>
+      </c>
+      <c r="E71" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>45989</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="2">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="C72" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D72" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202511</v>
+      </c>
+      <c r="E72" t="s">
         <v>19</v>
       </c>
-      <c r="C72" t="s">
+      <c r="F72" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>45991</v>
       </c>
-      <c r="B73" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B73" s="2">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="C73" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D73" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202511</v>
+      </c>
+      <c r="E73" t="s">
+        <v>7</v>
+      </c>
+      <c r="F73" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>46006</v>
       </c>
-      <c r="B74" t="s">
-        <v>5</v>
-      </c>
-      <c r="C74" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B74" s="2">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="C74" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D74" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202512</v>
+      </c>
+      <c r="E74" t="s">
+        <v>5</v>
+      </c>
+      <c r="F74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>46016</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="2">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="C75" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D75" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202512</v>
+      </c>
+      <c r="E75" t="s">
         <v>20</v>
       </c>
-      <c r="C75" t="s">
+      <c r="F75" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>46022</v>
       </c>
-      <c r="B76" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B76" s="2">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="C76" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D76" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202512</v>
+      </c>
+      <c r="E76" t="s">
+        <v>7</v>
+      </c>
+      <c r="F76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>46022</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="C77" s="2">
+        <f t="shared" si="4"/>
+        <v>2025</v>
+      </c>
+      <c r="D77" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202512</v>
+      </c>
+      <c r="E77" t="s">
         <v>21</v>
       </c>
-      <c r="C77" t="s">
+      <c r="F77" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>46023</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="C78" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D78" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202601</v>
+      </c>
+      <c r="E78" t="s">
         <v>3</v>
       </c>
-      <c r="C78" t="s">
+      <c r="F78" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>46037</v>
       </c>
-      <c r="B79" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B79" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="C79" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D79" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202601</v>
+      </c>
+      <c r="E79" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>46053</v>
       </c>
-      <c r="B80" t="s">
-        <v>7</v>
-      </c>
-      <c r="C80" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B80" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="C80" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D80" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202601</v>
+      </c>
+      <c r="E80" t="s">
+        <v>7</v>
+      </c>
+      <c r="F80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>46067</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="2">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="C81" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D81" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202602</v>
+      </c>
+      <c r="E81" t="s">
         <v>8</v>
       </c>
-      <c r="C81" t="s">
+      <c r="F81" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>46068</v>
       </c>
-      <c r="B82" t="s">
-        <v>5</v>
-      </c>
-      <c r="C82" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B82" s="2">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="C82" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D82" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202602</v>
+      </c>
+      <c r="E82" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>46081</v>
       </c>
-      <c r="B83" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B83" s="2">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="C83" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D83" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202602</v>
+      </c>
+      <c r="E83" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>46096</v>
       </c>
-      <c r="B84" t="s">
-        <v>5</v>
-      </c>
-      <c r="C84" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B84" s="2">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="C84" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D84" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202603</v>
+      </c>
+      <c r="E84" t="s">
+        <v>5</v>
+      </c>
+      <c r="F84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>46110</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="2">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="C85" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D85" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202603</v>
+      </c>
+      <c r="E85" t="s">
         <v>10</v>
       </c>
-      <c r="C85" t="s">
+      <c r="F85" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>46112</v>
       </c>
-      <c r="B86" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B86" s="2">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="C86" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D86" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202603</v>
+      </c>
+      <c r="E86" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>46114</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="C87" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D87" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202604</v>
+      </c>
+      <c r="E87" t="s">
         <v>12</v>
       </c>
-      <c r="C87" t="s">
+      <c r="F87" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>46115</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="C88" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D88" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202604</v>
+      </c>
+      <c r="E88" t="s">
         <v>13</v>
       </c>
-      <c r="C88" t="s">
+      <c r="F88" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>46127</v>
       </c>
-      <c r="B89" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B89" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="C89" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D89" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202604</v>
+      </c>
+      <c r="E89" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>46142</v>
       </c>
-      <c r="B90" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B90" s="2">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="C90" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D90" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202604</v>
+      </c>
+      <c r="E90" t="s">
+        <v>7</v>
+      </c>
+      <c r="F90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>46152</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="2">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="C91" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D91" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202605</v>
+      </c>
+      <c r="E91" t="s">
         <v>14</v>
       </c>
-      <c r="C91" t="s">
+      <c r="F91" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>46157</v>
       </c>
-      <c r="B92" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B92" s="2">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="C92" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D92" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202605</v>
+      </c>
+      <c r="E92" t="s">
+        <v>5</v>
+      </c>
+      <c r="F92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>46173</v>
       </c>
-      <c r="B93" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B93" s="2">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="C93" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D93" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202605</v>
+      </c>
+      <c r="E93" t="s">
+        <v>7</v>
+      </c>
+      <c r="F93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>46188</v>
       </c>
-      <c r="B94" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B94" s="2">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="C94" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D94" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202606</v>
+      </c>
+      <c r="E94" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>46194</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="2">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="C95" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D95" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202606</v>
+      </c>
+      <c r="E95" t="s">
         <v>15</v>
       </c>
-      <c r="C95" t="s">
+      <c r="F95" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>46203</v>
       </c>
-      <c r="B96" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B96" s="2">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="C96" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D96" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202606</v>
+      </c>
+      <c r="E96" t="s">
+        <v>7</v>
+      </c>
+      <c r="F96" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>46218</v>
       </c>
-      <c r="B97" t="s">
-        <v>5</v>
-      </c>
-      <c r="C97" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B97" s="2">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="C97" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D97" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202607</v>
+      </c>
+      <c r="E97" t="s">
+        <v>5</v>
+      </c>
+      <c r="F97" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>46231</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="2">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="C98" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D98" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202607</v>
+      </c>
+      <c r="E98" t="s">
         <v>16</v>
       </c>
-      <c r="C98" t="s">
+      <c r="F98" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>46232</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="2">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="C99" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D99" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202607</v>
+      </c>
+      <c r="E99" t="s">
         <v>16</v>
       </c>
-      <c r="C99" t="s">
+      <c r="F99" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>46234</v>
       </c>
-      <c r="B100" t="s">
-        <v>7</v>
-      </c>
-      <c r="C100" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B100" s="2">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="C100" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D100" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202607</v>
+      </c>
+      <c r="E100" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>46249</v>
       </c>
-      <c r="B101" t="s">
-        <v>5</v>
-      </c>
-      <c r="C101" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B101" s="2">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="C101" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D101" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202608</v>
+      </c>
+      <c r="E101" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>46265</v>
       </c>
-      <c r="B102" t="s">
-        <v>7</v>
-      </c>
-      <c r="C102" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B102" s="2">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="C102" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D102" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202608</v>
+      </c>
+      <c r="E102" t="s">
+        <v>7</v>
+      </c>
+      <c r="F102" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>46280</v>
       </c>
-      <c r="B103" t="s">
-        <v>5</v>
-      </c>
-      <c r="C103" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B103" s="2">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="C103" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D103" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202609</v>
+      </c>
+      <c r="E103" t="s">
+        <v>5</v>
+      </c>
+      <c r="F103" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>46280</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="C104" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D104" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202609</v>
+      </c>
+      <c r="E104" t="s">
         <v>17</v>
       </c>
-      <c r="C104" t="s">
+      <c r="F104" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>46295</v>
       </c>
-      <c r="B105" t="s">
-        <v>7</v>
-      </c>
-      <c r="C105" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B105" s="2">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="C105" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D105" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202609</v>
+      </c>
+      <c r="E105" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>46310</v>
       </c>
-      <c r="B106" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B106" s="2">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="C106" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D106" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202610</v>
+      </c>
+      <c r="E106" t="s">
+        <v>5</v>
+      </c>
+      <c r="F106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>46326</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="2">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="C107" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D107" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202610</v>
+      </c>
+      <c r="E107" t="s">
         <v>18</v>
       </c>
-      <c r="C107" t="s">
+      <c r="F107" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>46326</v>
       </c>
-      <c r="B108" t="s">
-        <v>7</v>
-      </c>
-      <c r="C108" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B108" s="2">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="C108" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D108" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202610</v>
+      </c>
+      <c r="E108" t="s">
+        <v>7</v>
+      </c>
+      <c r="F108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>46341</v>
       </c>
-      <c r="B109" t="s">
-        <v>5</v>
-      </c>
-      <c r="C109" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B109" s="2">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="C109" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D109" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202611</v>
+      </c>
+      <c r="E109" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>46353</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="2">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="C110" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D110" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202611</v>
+      </c>
+      <c r="E110" t="s">
         <v>19</v>
       </c>
-      <c r="C110" t="s">
+      <c r="F110" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>46356</v>
       </c>
-      <c r="B111" t="s">
-        <v>7</v>
-      </c>
-      <c r="C111" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B111" s="2">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="C111" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D111" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202611</v>
+      </c>
+      <c r="E111" t="s">
+        <v>7</v>
+      </c>
+      <c r="F111" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>46371</v>
       </c>
-      <c r="B112" t="s">
-        <v>5</v>
-      </c>
-      <c r="C112" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B112" s="2">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="C112" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D112" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202612</v>
+      </c>
+      <c r="E112" t="s">
+        <v>5</v>
+      </c>
+      <c r="F112" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>46381</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="2">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="C113" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D113" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202612</v>
+      </c>
+      <c r="E113" t="s">
         <v>20</v>
       </c>
-      <c r="C113" t="s">
+      <c r="F113" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>46387</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="2">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="C114" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D114" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202612</v>
+      </c>
+      <c r="E114" t="s">
         <v>21</v>
       </c>
-      <c r="C114" t="s">
+      <c r="F114" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>46387</v>
       </c>
-      <c r="B115" t="s">
-        <v>7</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="B115" s="2">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="C115" s="2">
+        <f t="shared" si="4"/>
+        <v>2026</v>
+      </c>
+      <c r="D115" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>202612</v>
+      </c>
+      <c r="E115" t="s">
+        <v>7</v>
+      </c>
+      <c r="F115" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010018451F55413CCE40B32872F2EE2F7B17" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="969693e52f69943e32048b02ca88382a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8574a8e8-5383-43f9-82c2-17454492c82a" xmlns:ns3="d25c0998-d329-4608-bd73-3e8a880c0119" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="069909415eb877d2dc8b3adebaeaef02" ns2:_="" ns3:_="">
     <xsd:import namespace="8574a8e8-5383-43f9-82c2-17454492c82a"/>
@@ -1934,15 +3422,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1955,13 +3434,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{978B99AA-7CF2-449C-8768-772697A1D2E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CFAC60B-6769-44B7-A349-FD7F8933EF26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CFAC60B-6769-44B7-A349-FD7F8933EF26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{978B99AA-7CF2-449C-8768-772697A1D2E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8574a8e8-5383-43f9-82c2-17454492c82a"/>
+    <ds:schemaRef ds:uri="d25c0998-d329-4608-bd73-3e8a880c0119"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFC98AE4-DA0F-44EB-ADA4-C2349CB022C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFC98AE4-DA0F-44EB-ADA4-C2349CB022C0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d25c0998-d329-4608-bd73-3e8a880c0119"/>
+    <ds:schemaRef ds:uri="8574a8e8-5383-43f9-82c2-17454492c82a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>